--- a/docs/station3/tripost_all_table_definitions.xlsx
+++ b/docs/station3/tripost_all_table_definitions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="10980" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="11640" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="users" sheetId="1" r:id="rId1"/>
@@ -219,10 +219,10 @@
     <t>body</t>
   </si>
   <si>
-    <t>follower_id</t>
-  </si>
-  <si>
-    <t>followed_id</t>
+    <t>following</t>
+  </si>
+  <si>
+    <t>followed</t>
   </si>
   <si>
     <t>day</t>

--- a/docs/station3/tripost_all_table_definitions.xlsx
+++ b/docs/station3/tripost_all_table_definitions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11640" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="11580" firstSheet="5" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="users" sheetId="1" r:id="rId1"/>
@@ -12,12 +12,14 @@
     <sheet name="likes" sheetId="3" r:id="rId3"/>
     <sheet name="comments" sheetId="4" r:id="rId4"/>
     <sheet name="follows" sheetId="5" r:id="rId5"/>
-    <sheet name="itineraries" sheetId="6" r:id="rId6"/>
-    <sheet name="photos" sheetId="7" r:id="rId7"/>
-    <sheet name="countries" sheetId="8" r:id="rId8"/>
-    <sheet name="styles" sheetId="9" r:id="rId9"/>
-    <sheet name="purposes" sheetId="10" r:id="rId10"/>
-    <sheet name="budgets" sheetId="11" r:id="rId11"/>
+    <sheet name="countries" sheetId="8" r:id="rId6"/>
+    <sheet name="styles" sheetId="9" r:id="rId7"/>
+    <sheet name="purposes" sheetId="10" r:id="rId8"/>
+    <sheet name="budgets" sheetId="11" r:id="rId9"/>
+    <sheet name="country_user" sheetId="12" r:id="rId10"/>
+    <sheet name="notifications" sheetId="13" r:id="rId11"/>
+    <sheet name="sessions" sheetId="14" r:id="rId12"/>
+    <sheet name="password_reset_tokens" sheetId="15" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="85">
   <si>
     <t>カラム名</t>
   </si>
@@ -84,88 +86,88 @@
     <t>username</t>
   </si>
   <si>
+    <t>VARCHAR(255)</t>
+  </si>
+  <si>
     <t>email</t>
   </si>
   <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>profile_image</t>
+  </si>
+  <si>
+    <t>bio</t>
+  </si>
+  <si>
+    <t>TEXT</t>
+  </si>
+  <si>
+    <t>email_verified_at</t>
+  </si>
+  <si>
+    <t>TIMESTAMP</t>
+  </si>
+  <si>
+    <t>remember_token</t>
+  </si>
+  <si>
     <t>VARCHAR(100)</t>
   </si>
   <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>VARCHAR(255)</t>
-  </si>
-  <si>
-    <t>profile_image</t>
-  </si>
-  <si>
-    <t>bio</t>
-  </si>
-  <si>
-    <t>TEXT</t>
-  </si>
-  <si>
-    <t>visited_countries</t>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>CURRENT_TIMESTAMP</t>
+  </si>
+  <si>
+    <t>updated_at</t>
+  </si>
+  <si>
+    <t>AUTO_INCREMENT</t>
+  </si>
+  <si>
+    <t>user_id</t>
+  </si>
+  <si>
+    <t>FK</t>
+  </si>
+  <si>
+    <t>users.id</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>subtitle</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>country_id</t>
   </si>
   <si>
     <t>BIGINT</t>
   </si>
   <si>
-    <t>FK</t>
-  </si>
-  <si>
     <t>countries.id</t>
   </si>
   <si>
-    <t>created_at</t>
-  </si>
-  <si>
-    <t>TIMESTAMP</t>
-  </si>
-  <si>
-    <t>CURRENT_TIMESTAMP</t>
-  </si>
-  <si>
-    <t>updated_at</t>
-  </si>
-  <si>
-    <t>AUTO_INCREMENT</t>
-  </si>
-  <si>
-    <t>user_id</t>
-  </si>
-  <si>
-    <t>users.id</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>subtitle</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>country_id</t>
-  </si>
-  <si>
     <t>region</t>
   </si>
   <si>
     <t>style_id</t>
   </si>
   <si>
-    <t xml:space="preserve"> "ソロ"</t>
-  </si>
-  <si>
     <t>styles.id</t>
   </si>
   <si>
     <t>period</t>
   </si>
   <si>
-    <t>DATE</t>
+    <t>VARCHAR(7)</t>
   </si>
   <si>
     <t>例：2025年8月</t>
@@ -183,9 +185,6 @@
     <t>purpose_id</t>
   </si>
   <si>
-    <t>"歴史・文化"</t>
-  </si>
-  <si>
     <t>purposes.id</t>
   </si>
   <si>
@@ -210,6 +209,15 @@
     <t>"非公開","公開"</t>
   </si>
   <si>
+    <t>trip_plan</t>
+  </si>
+  <si>
+    <t>JSON</t>
+  </si>
+  <si>
+    <t>photos</t>
+  </si>
+  <si>
     <t>post_id</t>
   </si>
   <si>
@@ -225,33 +233,6 @@
     <t>followed</t>
   </si>
   <si>
-    <t>day</t>
-  </si>
-  <si>
-    <t>time</t>
-  </si>
-  <si>
-    <t>TIME</t>
-  </si>
-  <si>
-    <t>place</t>
-  </si>
-  <si>
-    <t>latitude</t>
-  </si>
-  <si>
-    <t>DOUBLE</t>
-  </si>
-  <si>
-    <t>longitude</t>
-  </si>
-  <si>
-    <t>memo</t>
-  </si>
-  <si>
-    <t>image_url</t>
-  </si>
-  <si>
     <t>name</t>
   </si>
   <si>
@@ -264,12 +245,6 @@
     <t>VARCHAR(8)</t>
   </si>
   <si>
-    <t>"solo"</t>
-  </si>
-  <si>
-    <t>"nature"</t>
-  </si>
-  <si>
     <t>min</t>
   </si>
   <si>
@@ -282,7 +257,43 @@
     <t>label</t>
   </si>
   <si>
-    <t>VARCHAR(10)</t>
+    <t>actor_id</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>notifiable_id</t>
+  </si>
+  <si>
+    <t>notifiable_type</t>
+  </si>
+  <si>
+    <t>read</t>
+  </si>
+  <si>
+    <t>TINYINT(1)</t>
+  </si>
+  <si>
+    <t>ip_address</t>
+  </si>
+  <si>
+    <t>VARCHAR(45)</t>
+  </si>
+  <si>
+    <t>user_agent</t>
+  </si>
+  <si>
+    <t>payload</t>
+  </si>
+  <si>
+    <t>LONGTEXT</t>
+  </si>
+  <si>
+    <t>last_activity</t>
+  </si>
+  <si>
+    <t>token</t>
   </si>
 </sst>
 </file>
@@ -650,7 +661,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -670,6 +681,79 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.35"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.35"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.35"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.35"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.35"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.35"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.35"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.35"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.35"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.35"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.35"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.35"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.35"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.35"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.35"/>
       </bottom>
       <diagonal/>
     </border>
@@ -795,7 +879,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -807,34 +891,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -919,9 +1003,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1270,7 +1368,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="18.4615384615385" customWidth="1"/>
@@ -1281,153 +1379,195 @@
     <col min="6" max="6" width="23.5384615384615" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="17.55" spans="1:6">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="A3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
+      <c r="B4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E5" t="s">
+      <c r="B5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
+      <c r="F5" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
+      <c r="B8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+      <c r="B9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F9" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
+      <c r="B11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B10" t="s">
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" t="s">
-        <v>28</v>
-      </c>
+      <c r="B12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1438,13 +1578,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="5"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="10.3076923076923" customWidth="1"/>
     <col min="2" max="2" width="22.6153846153846" customWidth="1"/>
-    <col min="3" max="3" width="8.46153846153846" customWidth="1"/>
-    <col min="5" max="6" width="22.9230769230769" customWidth="1"/>
+    <col min="6" max="6" width="22.9230769230769" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1478,22 +1617,61 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>76</v>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1501,13 +1679,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="10.3076923076923" customWidth="1"/>
+    <col min="1" max="1" width="15.7692307692308" customWidth="1"/>
     <col min="2" max="2" width="22.6153846153846" customWidth="1"/>
-    <col min="3" max="3" width="8.46153846153846" customWidth="1"/>
-    <col min="5" max="6" width="22.9230769230769" customWidth="1"/>
+    <col min="6" max="6" width="22.9230769230769" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1541,29 +1718,183 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="12.7692307692308" customWidth="1"/>
+    <col min="2" max="2" width="22.6153846153846" customWidth="1"/>
+    <col min="6" max="6" width="22.9230769230769" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="s">
         <v>3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s">
         <v>79</v>
-      </c>
-      <c r="B4" t="s">
-        <v>78</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -1577,17 +1908,103 @@
         <v>80</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>81</v>
       </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>3</v>
+      <c r="B6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="11.0769230769231" customWidth="1"/>
+    <col min="2" max="2" width="22.6153846153846" customWidth="1"/>
+    <col min="6" max="6" width="22.9230769230769" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1595,7 +2012,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="19.3076923076923" customWidth="1"/>
@@ -1637,18 +2054,18 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -1657,12 +2074,12 @@
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
@@ -1673,7 +2090,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
@@ -1687,10 +2104,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -1701,21 +2118,21 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -1729,16 +2146,13 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
         <v>40</v>
@@ -1777,80 +2191,111 @@
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>30</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
       </c>
       <c r="E12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" t="s">
         <v>48</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" t="s">
         <v>50</v>
       </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" t="s">
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>52</v>
       </c>
-      <c r="B14" t="s">
+      <c r="F14" t="s">
         <v>53</v>
       </c>
-      <c r="E14" t="s">
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" t="s">
         <v>55</v>
-      </c>
-      <c r="B15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>57</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="E17" t="s">
-        <v>28</v>
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1862,8 +2307,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="22.6153846153846" customWidth="1"/>
@@ -1902,46 +2347,57 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
         <v>27</v>
       </c>
-      <c r="E5" t="s">
-        <v>28</v>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1994,43 +2450,43 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -2041,13 +2497,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
         <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2059,8 +2515,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.3076923076923" customWidth="1"/>
     <col min="2" max="2" width="22.6153846153846" customWidth="1"/>
@@ -2100,46 +2556,57 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
         <v>27</v>
       </c>
-      <c r="E5" t="s">
-        <v>28</v>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2151,8 +2618,8 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="10.3076923076923" customWidth="1"/>
     <col min="2" max="2" width="22.6153846153846" customWidth="1"/>
@@ -2174,7 +2641,9 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1"/>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
@@ -2190,40 +2659,34 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -2234,58 +2697,24 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2295,175 +2724,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="5"/>
-  <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="22.6153846153846" customWidth="1"/>
-    <col min="3" max="3" width="8.46153846153846" customWidth="1"/>
-    <col min="4" max="4" width="7.38461538461539" customWidth="1"/>
-    <col min="5" max="6" width="22.9230769230769" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="5"/>
-  <cols>
-    <col min="1" max="1" width="10.3076923076923" customWidth="1"/>
-    <col min="2" max="2" width="22.6153846153846" customWidth="1"/>
-    <col min="3" max="3" width="8.46153846153846" customWidth="1"/>
-    <col min="4" max="4" width="7.38461538461539" customWidth="1"/>
-    <col min="5" max="6" width="22.9230769230769" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F3"/>
@@ -2506,18 +2766,169 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="10.3076923076923" customWidth="1"/>
+    <col min="2" max="2" width="22.6153846153846" customWidth="1"/>
+    <col min="3" max="3" width="8.46153846153846" customWidth="1"/>
+    <col min="5" max="6" width="22.9230769230769" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="10.3076923076923" customWidth="1"/>
+    <col min="2" max="2" width="22.6153846153846" customWidth="1"/>
+    <col min="3" max="3" width="8.46153846153846" customWidth="1"/>
+    <col min="5" max="6" width="22.9230769230769" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
         <v>71</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>75</v>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
